--- a/data/Buff.xlsx
+++ b/data/Buff.xlsx
@@ -533,257 +533,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>set&lt;string&gt;</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>set&lt;string&gt;</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>set&lt;string&gt;</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>repeated double</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>designer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>expr:double expr_params:level,health</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>expr:double</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
@@ -792,40 +544,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>#pragma once
-enum eBuffType {
-    // 控制类 Buff
-    kBuffTypeMovementSpeedReduction = 0,           // 移动速度减速
-    kBuffTypeAttackSpeedSlow = 1,                  // 攻击速度减速
-    kBuffTypeCastSpeedSlow = 2,                    // 技能施放速度减速
-    kBuffTypeGlobalSlow = 3,                       // 全局减速（移动、攻击、施法等都减速）
-    // 属性增强类 Buff
-    kBuffTypeIncreaseAttack = 10,                  // 增加攻击力
-    kBuffTypeIncreaseDefense = 11,                 // 增加防御力
-    kBuffTypeIncreaseHealth = 12,                  // 增加最大生命值
-    kBuffTypeMovementSpeedBoost = 13,              // 提高移动速度
-    kBuffTypeIncreaseCriticalChance = 14,          // 提高暴击率
-    // 防御类 Buff
-    kBuffTypeDamageReduction = 20,                 // 减少受到的伤害
-    kBuffTypeShield = 21,                          // 获得护盾（吸收伤害）
-    // 特殊类 Buff
-    kBuffTypeStun = 30,                            // 晕眩，无法行动
-    kBuffTypeSilence = 31,                         // 沉默，无法施放技能
-    kBuffTypeInvincibility = 32,                   // 无敌，免疫所有伤害
-    kBuffTypeStealth = 33,                         // 隐身，无法被敌人发现
-    kBuffTypeImmunity = 34,                        // 免疫buff
-    kBuffTypeDispel = 35,                          // 驱散，移除buff或debuff
-    kBuffTypeNextBasicAttack = 36,                 // 下一次普攻，造成额外效果
-    // 持续恢复类 Buff
-    kBuffTypeHealthRegeneration = 40,              // 持续恢复生命值
-    kBuffTypeManaRegeneration = 41,                // 持续恢复法力值
-    kBuffTypeHealthRegenerationBasedOnLostHealth = 42, // 根据已损失生命值的每秒回复
-    kBuffTypeNoDamageOrSkillHitInLastSeconds = 43, // 若在过去s秒内，没有受到伤害或被技能命中
-    // Debuff 类
-    kBuffTypePoison = 50,                          // 中毒，持续扣除生命值
-    kBuffTypeBurn = 51,                            // 燃烧，持续受到火焰伤害
-    kBuffTypeFreeze = 52,                          // 冰冻，无法行动
-};</t>
+          <t>#pragma once</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
